--- a/up.xlsx
+++ b/up.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="660" windowWidth="27735" windowHeight="13500"/>
+    <workbookView xWindow="510" yWindow="585" windowWidth="27735" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="편입자산정보" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>종목명</t>
   </si>
@@ -49,6 +49,15 @@
     <t>무디스: Aa2 / S&amp;P: AA</t>
   </si>
   <si>
+    <t>선취보수율</t>
+  </si>
+  <si>
+    <t>후취보수율</t>
+  </si>
+  <si>
+    <t>거래통화</t>
+  </si>
+  <si>
     <t>- 구분</t>
   </si>
   <si>
@@ -59,6 +68,9 @@
   </si>
   <si>
     <t>3. 날짜계산기준: 미국 30/360=1, ACT/ACT=2, ACT/360=3, ACT/365=4, 유럽 30/360=5</t>
+  </si>
+  <si>
+    <t>4. 거래통화: USD=1, EUR=2, CNY=3, JPY=4, KRW=0</t>
   </si>
 </sst>
 </file>
@@ -66,11 +78,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -105,14 +117,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -191,6 +203,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,6 +238,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -259,20 +273,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -394,21 +404,59 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="17.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="17.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -424,7 +472,7 @@
         <v>35156</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="17.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -432,7 +480,7 @@
         <v>71681</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="17.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -440,7 +488,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="17.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -448,21 +496,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="17.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="17.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -470,7 +518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="17.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -478,28 +526,61 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="10" spans="1:2" ht="17.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25">
       <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25">
       <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25">
       <c r="A14" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="17.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="17.25">
+      <c r="A18" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B5 A8:B9 A6 A11:B18 A10 A7" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>